--- a/docs/manuscript_development/generated_assets/table2_clinical_step_contrasts.xlsx
+++ b/docs/manuscript_development/generated_assets/table2_clinical_step_contrasts.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,29 +429,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Outcome channel</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Clinical increment</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Adjusted rSO2 difference, percentage points</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>95% CI</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Adjusted rSO2 difference, median percentage points</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>IQR across 20 segments</t>
         </is>
       </c>
     </row>
@@ -461,12 +473,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.41 to 3.33</t>
+          <t>2.17 to 2.99</t>
         </is>
       </c>
     </row>
@@ -483,17 +495,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+10 percentage points</t>
+          <t>+5 percentage points</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.49 to 0.12</t>
+          <t>-0.12 to 0.36</t>
         </is>
       </c>
     </row>
@@ -515,12 +527,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.16 to 0.35</t>
+          <t>0.01 to 0.30</t>
         </is>
       </c>
     </row>
@@ -542,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.64 to 3.28</t>
+          <t>2.03 to 2.84</t>
         </is>
       </c>
     </row>
@@ -564,17 +576,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+10 percentage points</t>
+          <t>+5 percentage points</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.46 to 0.37</t>
+          <t>-0.09 to 0.39</t>
         </is>
       </c>
     </row>
@@ -596,12 +608,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.25 to 0.87</t>
+          <t>-0.09 to 0.62</t>
         </is>
       </c>
     </row>
@@ -623,12 +635,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.68 to 1.16</t>
+          <t>1.12 to 1.39</t>
         </is>
       </c>
     </row>
@@ -645,17 +657,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+10 percentage points</t>
+          <t>+5 percentage points</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.11 to 0.46</t>
+          <t>-0.07 to 0.12</t>
         </is>
       </c>
     </row>
@@ -677,12 +689,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.03 to 0.30</t>
+          <t>0.12 to 0.38</t>
         </is>
       </c>
     </row>
